--- a/data/samples/DEMO04.xlsx
+++ b/data/samples/DEMO04.xlsx
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>66200</v>
+        <v>65571</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>39720</v>
+        <v>39343</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25800</v>
+        <v>26429</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>36410</v>
+        <v>36064</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>67400</v>
+        <v>66010</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>40440</v>
+        <v>39606</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>26600</v>
+        <v>27990</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>37070</v>
+        <v>36306</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
